--- a/01_Investment_Banking/instances/public_microsoft_linkedin_2016.xlsx
+++ b/01_Investment_Banking/instances/public_microsoft_linkedin_2016.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -40,9 +40,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="295">
-  <si>
-    <t xml:space="preserve">[TICKER] — Company Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="296">
+  <si>
+    <t xml:space="preserve">Microsoft acquisition of LinkedIn</t>
   </si>
   <si>
     <t xml:space="preserve">Sector:</t>
@@ -643,6 +643,9 @@
   </si>
   <si>
     <t xml:space="preserve">Implied value/share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast base (IS!E5)</t>
   </si>
   <si>
     <t xml:space="preserve">Comparable Companies</t>
@@ -1141,52 +1144,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1194,7 +1193,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1202,7 +1201,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1210,103 +1209,103 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1390,34 +1389,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1563,120 +1562,120 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D20"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1686,7 +1685,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1700,53 +1699,53 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:H13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C4" s="16" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="H4" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="20" t="n">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="32" t="n">
@@ -1759,17 +1758,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="20" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="32" t="n">
@@ -1782,17 +1781,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C7" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="20" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="32" t="n">
@@ -1805,17 +1804,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="20" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="32" t="n">
@@ -1828,17 +1827,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="20" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="32" t="n">
@@ -1851,17 +1850,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="20" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="32" t="n">
@@ -1874,17 +1873,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="20" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="32" t="n">
@@ -1897,9 +1896,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
-        <v>210</v>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="C13" s="30" t="n">
         <f aca="false">MEDIAN(C5:C12)</f>
@@ -1929,7 +1928,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1943,21 +1942,21 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C4" s="35" t="n">
         <v>0.015</v>
@@ -1975,110 +1974,110 @@
         <v>0.035</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="35" t="n">
         <v>0.08</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="35" t="n">
         <v>0.09</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="35" t="n">
         <v>0.1</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="35" t="n">
         <v>0.11</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="35" t="n">
         <v>0.12</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2092,112 +2091,112 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:F14"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F4" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="36" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="36"/>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
       <c r="E6" s="36"/>
       <c r="F6" s="36"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="36"/>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="36"/>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="36"/>
       <c r="C9" s="36"/>
       <c r="D9" s="36"/>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="36"/>
       <c r="C10" s="36"/>
       <c r="D10" s="36"/>
       <c r="E10" s="36"/>
       <c r="F10" s="36"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
       <c r="F11" s="36"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="36"/>
       <c r="C12" s="36"/>
       <c r="D12" s="36"/>
       <c r="E12" s="36"/>
       <c r="F12" s="36"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="36"/>
       <c r="C13" s="36"/>
       <c r="D13" s="36"/>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
       <c r="D14" s="36"/>
@@ -2207,7 +2206,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2221,231 +2220,231 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E32"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="16" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="E4" s="15" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="20" t="n">
         <v>26200</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="20" t="n">
         <v>26200</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>230</v>
       </c>
-      <c r="C6" s="37" t="n">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="E6" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="C7" s="37" t="n">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="E7" s="0" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C8" s="37" t="n">
         <v>133.673469</v>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="37" t="n">
         <v>133.673469</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+      <c r="E8" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="C9" s="37" t="n">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="20" t="n">
         <v>196</v>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="20" t="n">
         <v>196</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="E9" s="0" t="s">
         <v>237</v>
       </c>
-      <c r="C10" s="17" t="n">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="16" t="n">
         <v>0.09</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="16" t="n">
         <v>0.09</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+      <c r="E10" s="0" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="16" t="n">
         <v>0.025</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="16" t="n">
         <v>0.025</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="E11" s="0" t="s">
         <v>240</v>
       </c>
-      <c r="C12" s="37" t="n">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+      <c r="E12" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="C13" s="37" t="n">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="20" t="n">
         <v>75</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="20" t="n">
         <v>65</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C14" s="37" t="n">
+      <c r="E13" s="0" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C15" s="37" t="n">
+      <c r="E14" s="0" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="20" t="n">
         <v>85</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="20" t="n">
         <v>55</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" s="37" t="n">
+      <c r="E15" s="0" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="D16" s="37" t="n">
+      <c r="D16" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C17" s="17" t="n">
+      <c r="E16" s="0" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="16" t="n">
         <v>0.3</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="16" t="n">
         <v>0.3</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
+      <c r="E17" s="0" t="s">
         <v>248</v>
       </c>
-      <c r="C18" s="17" t="n">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="s">
+      <c r="E18" s="0" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
         <v>198</v>
       </c>
       <c r="C21" s="24" t="n">
@@ -2457,9 +2456,9 @@
         <v>26100</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="s">
-        <v>250</v>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
+        <v>251</v>
       </c>
       <c r="C22" s="24" t="n">
         <f aca="false">IFERROR(C21/C8,0)</f>
@@ -2470,22 +2469,22 @@
         <v>195.251908963326</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C23" s="39" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="C23" s="38" t="n">
         <f aca="false">IFERROR(C9/C22-1,0)</f>
         <v>0.0038314147126437</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D23" s="38" t="n">
         <f aca="false">IFERROR(D9/D22-1,0)</f>
         <v>0.0038314147126437</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="1" t="s">
-        <v>252</v>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="s">
+        <v>253</v>
       </c>
       <c r="C24" s="24" t="n">
         <f aca="false">C12/(1+C10)+C13/(1+C10)^2+C14/(1+C10)^3+C15/(1+C10)^4+C16/(1+C10)^5</f>
@@ -2496,8 +2495,8 @@
         <v>236.720347775732</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="1" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="s">
         <v>193</v>
       </c>
       <c r="C25" s="24" t="n">
@@ -2509,8 +2508,8 @@
         <v>788.461538461538</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="24" t="n">
@@ -2522,9 +2521,9 @@
         <v>512.445900735234</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="1" t="s">
-        <v>253</v>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0" t="s">
+        <v>254</v>
       </c>
       <c r="C27" s="24" t="n">
         <f aca="false">IF(AND(ISNUMBER(C24),ISNUMBER(C26)),C24+C26,"-")</f>
@@ -2535,9 +2534,9 @@
         <v>749.166248510966</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="1" t="s">
-        <v>254</v>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="0" t="s">
+        <v>255</v>
       </c>
       <c r="C28" s="24" t="n">
         <f aca="false">IF(ISNUMBER(C27),C27-C6+C7,"-")</f>
@@ -2548,9 +2547,9 @@
         <v>649.166248510966</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="1" t="s">
-        <v>255</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="0" t="s">
+        <v>256</v>
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">IF(ISNUMBER(C28),C28/C8,"-")</f>
@@ -2561,28 +2560,28 @@
         <v>4.85635820905467</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C30" s="39" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="C30" s="38" t="n">
         <f aca="false">IF(ISNUMBER(C29),ABS(C29-C22)/MAX(ABS(C22),1),"-")</f>
         <v>0.956696036382493</v>
       </c>
-      <c r="D30" s="39" t="n">
+      <c r="D30" s="38" t="n">
         <f aca="false">IF(ISNUMBER(D29),ABS(D29-D22)/MAX(ABS(D22),1),"-")</f>
         <v>0.975127729942109</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2596,113 +2595,113 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E18"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" s="16" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" s="37" t="n">
+      <c r="E4" s="15" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="20" t="n">
         <v>16800</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="20" t="n">
         <v>16800</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C6" s="38" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="C6" s="37" t="n">
         <v>8000</v>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="37" t="n">
         <v>8000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="37" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" s="20" t="n">
         <v>-164.8</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="20" t="n">
         <v>-164.8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C8" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>263</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="20" t="n">
         <v>592.5</v>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="20" t="n">
         <v>592.5</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
         <v>265</v>
       </c>
-      <c r="C11" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="C10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>266</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>267</v>
       </c>
       <c r="C14" s="24" t="n">
         <f aca="false">IFERROR(C5/C6,0)</f>
@@ -2713,9 +2712,9 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
-        <v>267</v>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>268</v>
       </c>
       <c r="C15" s="24" t="n">
         <f aca="false">C5+C7+C8-C9</f>
@@ -2726,9 +2725,9 @@
         <v>16042.7</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="s">
-        <v>268</v>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
+        <v>269</v>
       </c>
       <c r="C16" s="24" t="n">
         <f aca="false">C6+C10</f>
@@ -2739,9 +2738,9 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="s">
-        <v>269</v>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>270</v>
       </c>
       <c r="C17" s="24" t="n">
         <f aca="false">IFERROR(C15/C16,0)</f>
@@ -2752,15 +2751,15 @@
         <v>2.0053375</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C18" s="39" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="C18" s="38" t="n">
         <f aca="false">IFERROR(C17/C14-1,0)</f>
         <v>-0.045077380952381</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="38" t="n">
         <f aca="false">IFERROR(D17/D14-1,0)</f>
         <v>-0.045077380952381</v>
       </c>
@@ -2768,7 +2767,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2782,36 +2781,36 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E8"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="48"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="D4" s="16" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="D4" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>274</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>275</v>
       </c>
       <c r="C5" s="24" t="n">
         <f aca="false">'Transaction Analysis'!C22</f>
@@ -2821,13 +2820,13 @@
         <f aca="false">'Transaction Analysis'!D22</f>
         <v>195.251908963326</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>255</v>
+      <c r="E5" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>256</v>
       </c>
       <c r="C6" s="24" t="n">
         <f aca="false">'Transaction Analysis'!C29</f>
@@ -2837,13 +2836,13 @@
         <f aca="false">'Transaction Analysis'!D29</f>
         <v>4.85635820905467</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>235</v>
+      <c r="E6" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>236</v>
       </c>
       <c r="C7" s="24" t="n">
         <f aca="false">'Transaction Analysis'!C9</f>
@@ -2853,30 +2852,30 @@
         <f aca="false">'Transaction Analysis'!D9</f>
         <v>196</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C8" s="39" t="n">
+      <c r="E7" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="38" t="n">
         <f aca="false">'Accretion Dilution'!C18</f>
         <v>-0.045077380952381</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="38" t="n">
         <f aca="false">'Accretion Dilution'!D18</f>
         <v>-0.045077380952381</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>278</v>
+      <c r="E8" s="0" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2890,38 +2889,38 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E12"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="54"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="D4" s="16" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="E4" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C5" s="40" t="n">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" s="39" t="n">
         <f aca="false">'Transaction Analysis'!C5-'Transaction Analysis'!C6+'Transaction Analysis'!C7-'Transaction Analysis'!C21</f>
         <v>0</v>
       </c>
@@ -2929,15 +2928,15 @@
         <f aca="false">IF(ABS(C5)&lt;0.01,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>284</v>
       </c>
-      <c r="C6" s="40" t="n">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6" s="39" t="n">
         <f aca="false">'Transaction Analysis'!C21-'Transaction Analysis'!C22*'Transaction Analysis'!C8</f>
         <v>0</v>
       </c>
@@ -2945,15 +2944,15 @@
         <f aca="false">IF(ABS(C6)&lt;0.01,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="E6" s="0" t="s">
         <v>286</v>
       </c>
-      <c r="C7" s="40" t="n">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" s="39" t="n">
         <f aca="false">'Transaction Analysis'!D10-'Transaction Analysis'!D11</f>
         <v>0.065</v>
       </c>
@@ -2961,15 +2960,15 @@
         <f aca="false">IF(C7&gt;0,"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="E7" s="0" t="s">
         <v>288</v>
       </c>
-      <c r="C8" s="40" t="n">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="39" t="n">
         <f aca="false">'Transaction Analysis'!D23</f>
         <v>0.0038314147126437</v>
       </c>
@@ -2977,15 +2976,15 @@
         <f aca="false">IF(C8&lt;='Transaction Analysis'!D17,"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+      <c r="E8" s="0" t="s">
         <v>290</v>
       </c>
-      <c r="C9" s="40" t="n">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="C9" s="39" t="n">
         <f aca="false">'Accretion Dilution'!D18</f>
         <v>-0.045077380952381</v>
       </c>
@@ -2993,15 +2992,15 @@
         <f aca="false">IF(C9&gt;='Accretion Dilution'!D11,"PASS","BREACH")</f>
         <v>BREACH</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="E9" s="0" t="s">
         <v>292</v>
       </c>
-      <c r="C10" s="40" t="n">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="C10" s="39" t="n">
         <f aca="false">'Transaction Analysis'!D30</f>
         <v>0.975127729942109</v>
       </c>
@@ -3009,15 +3008,15 @@
         <f aca="false">IF(AND(ISNUMBER(C10),C10&lt;='Transaction Analysis'!D18),"PASS","BREACH")</f>
         <v>BREACH</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+      <c r="E10" s="0" t="s">
         <v>294</v>
       </c>
-      <c r="C12" s="41" t="str">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C12" s="40" t="str">
         <f aca="false">IF(COUNTIF(D5:D10,"FAIL")+COUNTIF(D5:D10,"BREACH")&gt;0,"BREACH",IF(COUNTIF(D5:D10,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
         <v>BREACH</v>
       </c>
@@ -3025,7 +3024,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3039,638 +3038,638 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F63"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10" t="s">
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="s">
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="14" t="s">
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="14" t="s">
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="1" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="1" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="1" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="1" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="1" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="1" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="1" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="13" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="14" t="s">
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="1" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="1" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="F39" s="15" t="s">
+      <c r="F39" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="1" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="1" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="F41" s="15" t="s">
+      <c r="F41" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="1" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="13" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="14" t="s">
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="1" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="F46" s="15" t="s">
+      <c r="F46" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="1" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="15" t="s">
+      <c r="F47" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="1" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="F48" s="15" t="s">
+      <c r="F48" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="1" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="F49" s="15" t="s">
+      <c r="F49" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="1" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="F50" s="15" t="s">
+      <c r="F50" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="13" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="14" t="s">
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="1" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="F54" s="15" t="s">
+      <c r="F54" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="1" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="F55" s="15" t="s">
+      <c r="F55" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="1" t="n">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="15" t="s">
+      <c r="F56" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="1" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="F57" s="15" t="s">
+      <c r="F57" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="1" t="n">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="F58" s="15" t="s">
+      <c r="F58" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="13" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="14" t="s">
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="1" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="0" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="1" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="0" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3720,7 +3719,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3734,230 +3733,230 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:I54"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10" t="s">
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="13" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D5" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D7" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H11" s="15"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H12" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H14" s="15"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H15" s="15"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H16" s="15"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H17" s="15"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H18" s="15"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H19" s="15"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H20" s="15"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H21" s="15"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H22" s="15"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H23" s="15"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H24" s="15"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H25" s="15"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H26" s="15"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H27" s="15"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H28" s="15"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H29" s="15"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H30" s="15"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H31" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H32" s="15"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H33" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H34" s="15"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H35" s="15"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H36" s="15"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H37" s="15"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H38" s="15"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H39" s="15"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H40" s="15"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H41" s="15"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H42" s="15"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H43" s="15"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H44" s="15"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H45" s="15"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H46" s="15"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H47" s="15"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H48" s="15"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H49" s="15"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H50" s="15"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H51" s="15"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H52" s="15"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H53" s="15"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H54" s="15"/>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="14"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H22" s="14"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="14"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="14"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="14"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="14"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="14"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="14"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="14"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="14"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="14"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="14"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="14"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H40" s="14"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H41" s="14"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="14"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H43" s="14"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H44" s="14"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H45" s="14"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H46" s="14"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H47" s="14"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="14"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H49" s="14"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H50" s="14"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H51" s="14"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H52" s="14"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H53" s="14"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H54" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3975,7 +3974,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3989,212 +3988,212 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10" t="s">
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J9" s="15"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J11" s="15"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J12" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J14" s="15"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J15" s="15"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J16" s="15"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J17" s="15"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J19" s="15"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J22" s="15"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J23" s="15"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J25" s="15"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J26" s="15"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J27" s="15"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J28" s="15"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J29" s="15"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J35" s="15"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J36" s="15"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J37" s="15"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J38" s="15"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J39" s="15"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J40" s="15"/>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J40" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4208,7 +4207,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4222,277 +4221,277 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:H14"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="15" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18" t="s">
+      <c r="C5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="18" t="s">
+      <c r="C6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="18" t="s">
+      <c r="C7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="18" t="s">
+      <c r="C8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="18" t="s">
+      <c r="C9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="18" t="s">
+      <c r="C10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="18" t="s">
+      <c r="C11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="18" t="s">
+      <c r="C12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C13" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="18" t="s">
+      <c r="C13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="18" t="s">
+      <c r="C14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="17" t="s">
         <v>128</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4506,52 +4505,52 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:I20"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="13"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="15" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
       <c r="F5" s="21" t="n">
         <f aca="false">E5*(1+Assumptions!C5)</f>
         <v>0</v>
@@ -4569,11 +4568,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="22" t="str">
         <f aca="false">IFERROR(D5/C5-1,"-")</f>
         <v>-</v>
@@ -4599,13 +4598,13 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="21" t="n">
         <f aca="false">F5*(1-Assumptions!C6)</f>
         <v>0</v>
@@ -4623,11 +4622,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="21"/>
+      <c r="C8" s="20"/>
       <c r="D8" s="21" t="n">
         <f aca="false">D5-D7</f>
         <v>0</v>
@@ -4653,11 +4652,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="22" t="str">
         <f aca="false">IFERROR(D8/D5,"-")</f>
         <v>-</v>
@@ -4683,13 +4682,13 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="21" t="n">
         <f aca="false">F5*Assumptions!C7</f>
         <v>0</v>
@@ -4707,13 +4706,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="21" t="n">
         <f aca="false">F8-F10</f>
         <v>0</v>
@@ -4731,13 +4730,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="22" t="str">
         <f aca="false">IFERROR(F11/F5,"-")</f>
         <v>-</v>
@@ -4755,13 +4754,13 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="21" t="n">
         <f aca="false">F5*Assumptions!C10*Assumptions!C9</f>
         <v>0</v>
@@ -4779,13 +4778,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="21" t="n">
         <f aca="false">F11-F13</f>
         <v>0</v>
@@ -4803,13 +4802,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="21" t="n">
         <f aca="false">$E$15</f>
         <v>0</v>
@@ -4827,13 +4826,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
       <c r="F16" s="21" t="n">
         <f aca="false">F14-F15</f>
         <v>0</v>
@@ -4851,13 +4850,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="21" t="n">
         <f aca="false">F16*Assumptions!C8</f>
         <v>0</v>
@@ -4875,13 +4874,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="21" t="n">
         <f aca="false">F16-F17</f>
         <v>0</v>
@@ -4899,13 +4898,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
       <c r="F19" s="21" t="n">
         <f aca="false">Assumptions!C12</f>
         <v>0</v>
@@ -4923,13 +4922,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="21" t="str">
         <f aca="false">IFERROR(F18/F19,"-")</f>
         <v>-</v>
@@ -4950,7 +4949,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4964,41 +4963,41 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="13"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="0" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
         <v>162</v>
       </c>
       <c r="C5" s="21"/>
@@ -5007,8 +5006,8 @@
       <c r="F5" s="21"/>
       <c r="G5" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>163</v>
       </c>
       <c r="C6" s="21"/>
@@ -5017,8 +5016,8 @@
       <c r="F6" s="21"/>
       <c r="G6" s="21"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
         <v>164</v>
       </c>
       <c r="C7" s="21"/>
@@ -5027,8 +5026,8 @@
       <c r="F7" s="21"/>
       <c r="G7" s="21"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C8" s="21" t="n">
@@ -5052,8 +5051,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C9" s="21"/>
@@ -5062,8 +5061,8 @@
       <c r="F9" s="21"/>
       <c r="G9" s="21"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
         <v>167</v>
       </c>
       <c r="C10" s="21"/>
@@ -5072,8 +5071,8 @@
       <c r="F10" s="21"/>
       <c r="G10" s="21"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C11" s="21" t="n">
@@ -5097,8 +5096,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
         <v>169</v>
       </c>
       <c r="C12" s="21"/>
@@ -5107,8 +5106,8 @@
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
         <v>170</v>
       </c>
       <c r="C13" s="21"/>
@@ -5117,8 +5116,8 @@
       <c r="F13" s="21"/>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C14" s="21" t="n">
@@ -5142,8 +5141,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
         <v>172</v>
       </c>
       <c r="C15" s="21"/>
@@ -5152,8 +5151,8 @@
       <c r="F15" s="21"/>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C16" s="21" t="n">
@@ -5177,8 +5176,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C17" s="21"/>
@@ -5187,7 +5186,7 @@
       <c r="F17" s="21"/>
       <c r="G17" s="21"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="23" t="s">
         <v>175</v>
       </c>
@@ -5215,7 +5214,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5229,41 +5228,41 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="13"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="0" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
         <v>158</v>
       </c>
       <c r="C5" s="21"/>
@@ -5281,8 +5280,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>177</v>
       </c>
       <c r="C6" s="21"/>
@@ -5300,8 +5299,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
         <v>178</v>
       </c>
       <c r="C7" s="21"/>
@@ -5310,8 +5309,8 @@
       <c r="F7" s="21"/>
       <c r="G7" s="21"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
         <v>179</v>
       </c>
       <c r="C8" s="21" t="n">
@@ -5335,8 +5334,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>180</v>
       </c>
       <c r="C9" s="21"/>
@@ -5345,8 +5344,8 @@
       <c r="F9" s="21"/>
       <c r="G9" s="21"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C10" s="21" t="n">
@@ -5370,8 +5369,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
         <v>182</v>
       </c>
       <c r="C11" s="21"/>
@@ -5380,8 +5379,8 @@
       <c r="F11" s="21"/>
       <c r="G11" s="21"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
         <v>183</v>
       </c>
       <c r="C12" s="21"/>
@@ -5390,8 +5389,8 @@
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
         <v>184</v>
       </c>
       <c r="C13" s="21" t="n">
@@ -5418,7 +5417,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5431,44 +5430,44 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:I14"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:I15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="16" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>188</v>
       </c>
       <c r="C5" s="26" t="n">
@@ -5491,15 +5490,15 @@
         <f aca="false">F5*(1+Assumptions!G5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="0" t="s">
         <v>189</v>
       </c>
       <c r="I5" s="27" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>190</v>
       </c>
       <c r="C6" s="28" t="n">
@@ -5522,15 +5521,15 @@
         <f aca="false">1/(1+$I$5)^(5)</f>
         <v>0.620921323059155</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="0" t="s">
         <v>191</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.025</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>192</v>
       </c>
       <c r="C7" s="29" t="n">
@@ -5553,7 +5552,7 @@
         <f aca="false">G5*G6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="0" t="s">
         <v>193</v>
       </c>
       <c r="I7" s="29" t="n">
@@ -5561,8 +5560,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="0" t="s">
         <v>194</v>
       </c>
       <c r="I8" s="29" t="n">
@@ -5570,8 +5569,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H9" s="0" t="s">
         <v>195</v>
       </c>
       <c r="I9" s="29" t="n">
@@ -5579,8 +5578,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H10" s="1" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="0" t="s">
         <v>196</v>
       </c>
       <c r="I10" s="30" t="n">
@@ -5588,16 +5587,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H11" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="0" t="s">
         <v>197</v>
       </c>
       <c r="I11" s="31" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H12" s="1" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="0" t="s">
         <v>198</v>
       </c>
       <c r="I12" s="30" t="n">
@@ -5605,27 +5604,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H13" s="1" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="0" t="s">
         <v>199</v>
       </c>
       <c r="I13" s="31" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H14" s="1" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="I14" s="30" t="n">
-        <f aca="false">I12/I13</f>
-        <v>0</v>
+      <c r="I14" s="30" t="str">
+        <f aca="false">IF(OR(IS!E5="",IS!E5=0),"n/a - no forecast base",I12/I13)</f>
+        <v>n/a - no forecast base</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="I15" s="2" t="str">
+        <f aca="false">IF(OR(IS!E5="",IS!E5=0),"MISSING - the DCF cannot value anything","present")</f>
+        <v>MISSING - the DCF cannot value anything</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
